--- a/tools/importer/reports/import-academics-directory.report.xlsx
+++ b/tools/importer/reports/import-academics-directory.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="63">
   <si>
     <t>_reportFile</t>
   </si>
@@ -106,7 +106,7 @@
     <t>index</t>
   </si>
   <si>
-    <t>2026-08-13T18:37:56.910Z</t>
+    <t>2026-08-13T19:09:49.009Z</t>
   </si>
   <si>
     <t>http://localhost:8082/</t>
@@ -148,7 +148,7 @@
     <t>audience-landing</t>
   </si>
   <si>
-    <t>2026-08-13T18:37:51.030Z</t>
+    <t>2026-08-13T19:09:54.180Z</t>
   </si>
   <si>
     <t>Prospective Students | U-M LSA U-M College of LSA</t>
@@ -157,16 +157,53 @@
     <t>http://localhost:8082/lsa/prospective-students.html</t>
   </si>
   <si>
+    <t>lsa/academics/departments-and-units.html.report.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.goto: net::ERR_CONNECTION_REFUSED at http://localhost:8082/lsa/academics/departments-and-units.html
+Call log:
+  - navigating to "http://localhost:8082/lsa/academics/departments-and-units.html", waiting until "domcontentloaded"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.goto: net::ERR_CONNECTION_REFUSED at http://localhost:8082/lsa/academics/departments-and-units.html
+Call log:
+  - navigating to "http://localhost:8082/lsa/academics/departments-and-units.html", waiting until "domcontentloaded"
+    at processUrl (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:469:18)
+    at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:696:22)</t>
+  </si>
+  <si>
+    <t>lsa/academics/departments-and-units.html</t>
+  </si>
+  <si>
+    <t>2026-08-14T14:25:12.612Z</t>
+  </si>
+  <si>
+    <t>http://localhost:8082/lsa/academics/departments-and-units.html</t>
+  </si>
+  <si>
+    <t>lsa/academics/departments-and-units.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>lsa/academics/departments-and-units</t>
+  </si>
+  <si>
+    <t>academics-listing</t>
+  </si>
+  <si>
+    <t>2026-08-14T14:25:35.515Z</t>
+  </si>
+  <si>
+    <t>Departments and Units | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
     <t>lsa/academics/majors-minors.report.json</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
     <t>lsa/academics/majors-minors</t>
-  </si>
-  <si>
-    <t>academics-listing</t>
   </si>
   <si>
     <t>2026-08-13T18:48:55.438Z</t>
@@ -564,13 +601,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="4" width="50" customWidth="1"/>
+    <col min="1" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="11" width="50" customWidth="1"/>
@@ -826,34 +862,104 @@
         <v>46</v>
       </c>
       <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
         <v>47</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
         <v>50</v>
       </c>
       <c r="J8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" t="s">
         <v>51</v>
       </c>
-      <c r="K8" t="s">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-academics-directory.report.xlsx
+++ b/tools/importer/reports/import-academics-directory.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="77">
   <si>
     <t>_reportFile</t>
   </si>
@@ -112,6 +112,27 @@
     <t>http://localhost:8082/</t>
   </si>
   <si>
+    <t>rc.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards"]</t>
+  </si>
+  <si>
+    <t>rc</t>
+  </si>
+  <si>
+    <t>unit-home</t>
+  </si>
+  <si>
+    <t>2026-08-14T14:54:44.130Z</t>
+  </si>
+  <si>
+    <t>Residential College | U-M LSA</t>
+  </si>
+  <si>
+    <t>http://localhost:8082/rc.html</t>
+  </si>
+  <si>
     <t>en/footer.report.json</t>
   </si>
   <si>
@@ -134,6 +155,27 @@
   </si>
   <si>
     <t>2026-08-13T18:11:39.386Z</t>
+  </si>
+  <si>
+    <t>english/undergraduate.report.json</t>
+  </si>
+  <si>
+    <t>["cards"]</t>
+  </si>
+  <si>
+    <t>english/undergraduate</t>
+  </si>
+  <si>
+    <t>department-landing</t>
+  </si>
+  <si>
+    <t>2026-08-14T15:34:11.176Z</t>
+  </si>
+  <si>
+    <t>Undergraduate Students | U-M LSA English Language and Literature</t>
+  </si>
+  <si>
+    <t>http://localhost:8082/english/undergraduate.html</t>
   </si>
   <si>
     <t>lsa/prospective-students.report.json</t>
@@ -194,7 +236,7 @@
     <t>academics-listing</t>
   </si>
   <si>
-    <t>2026-08-14T14:25:35.515Z</t>
+    <t>2026-08-14T15:34:16.482Z</t>
   </si>
   <si>
     <t>Departments and Units | U-M LSA U-M College of LSA</t>
@@ -601,13 +643,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="11" width="50" customWidth="1"/>
   </cols>
@@ -757,7 +799,7 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -766,7 +808,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
         <v>33</v>
@@ -775,21 +817,21 @@
         <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K5" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -801,10 +843,10 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
         <v>22</v>
@@ -813,7 +855,7 @@
         <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J6" t="s">
         <v>12</v>
@@ -824,10 +866,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -836,25 +878,25 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
         <v>22</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J7" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -862,42 +904,42 @@
         <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
         <v>48</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s">
         <v>49</v>
-      </c>
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
       </c>
       <c r="I8" t="s">
         <v>50</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -909,57 +951,127 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
         <v>22</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" t="s">
         <v>22</v>
       </c>
-      <c r="H10" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" t="s">
-        <v>61</v>
-      </c>
-      <c r="K10" t="s">
-        <v>62</v>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
